--- a/output/details/2026-05-05/preprocessed_data.xlsx
+++ b/output/details/2026-05-05/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46147</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1079781561525337</v>
+        <v>-0.1075103944083455</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2041150155348604</v>
+        <v>-0.1321931460094877</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2038196255737078</v>
+        <v>-0.1319301065934766</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1339404987339735</v>
+        <v>0.01600335934347176</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001703802050983955</v>
+        <v>0.001704167869406889</v>
       </c>
       <c r="G2" t="n">
-        <v>1.771032568944502</v>
+        <v>2.354592079261975</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4634137863148057</v>
+        <v>-0.2565322274880478</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
